--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487513_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487513_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3492</v>
+        <v>2.6081</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4838</v>
+        <v>2.0745</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1346</v>
+        <v>0.5336</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5328000000000001</v>
@@ -610,13 +610,13 @@
         <v>1.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3749</v>
+        <v>-0.116</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7575</v>
+        <v>0.3482</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1325</v>
+        <v>-0.4642</v>
       </c>
       <c r="V2" t="n">
         <v>4.0403</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>J. SEARA GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8346</v>
+        <v>0.4602</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8745000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7091</v>
+        <v>0.3768</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0038</v>
+        <v>0.1769</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0014</v>
+        <v>0.1364</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0052</v>
+        <v>0.0404</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5056</v>
+        <v>0.0404</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9254</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5803</v>
+        <v>0.0404</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5094</v>
+        <v>0.1364</v>
       </c>
       <c r="N3" t="n">
-        <v>0.076</v>
+        <v>0.1364</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5855</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1336</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0135</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4781</v>
+        <v>0.0429</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5354</v>
+        <v>0.0446</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SEARA GONZALEZ</t>
+          <t>B. RODRÍGUEZ HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3311</v>
+        <v>-0.0606</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.019</v>
+        <v>-0.9629</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3501</v>
+        <v>0.9024</v>
       </c>
       <c r="G4" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.2031</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.1769</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.1364</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0404</v>
-      </c>
       <c r="J4" t="n">
-        <v>0.0404</v>
+        <v>-0.6418</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-0.6822</v>
       </c>
       <c r="L4" t="n">
         <v>0.0404</v>
       </c>
       <c r="M4" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4791</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.1364</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.1364</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0416</v>
+        <v>-0.2877</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0594</v>
+        <v>-0.1253</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0178</v>
+        <v>-0.1625</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2516</v>
+        <v>-0.3807</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8631</v>
+        <v>-0.9654</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6115</v>
+        <v>0.5848</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3689</v>
@@ -844,13 +844,13 @@
         <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5874</v>
+        <v>0.4583</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4446</v>
+        <v>0.3423</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1427</v>
+        <v>0.116</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6659</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. RODRÍGUEZ HERNÁNDEZ</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3897</v>
+        <v>-0.7819</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3723</v>
+        <v>-1.2079</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9826</v>
+        <v>0.426</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0262</v>
+        <v>-0.0038</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2031</v>
+        <v>1.0014</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1769</v>
+        <v>-1.0052</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6418</v>
+        <v>1.5056</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6822</v>
+        <v>0.9254</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>0.5803</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6156</v>
+        <v>-1.5094</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4791</v>
+        <v>0.076</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1364</v>
+        <v>-1.5855</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1958</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1958</v>
+        <v>-3.1336</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3917</v>
+        <v>1.9585</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6169</v>
+        <v>0.397</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5346</v>
+        <v>0.1447</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0823</v>
+        <v>0.2523</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0576</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0576</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5717</v>
+        <v>-1.404</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4392</v>
+        <v>0.6604</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0109</v>
+        <v>-2.0644</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4207</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2074</v>
+        <v>-0.0397</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0306</v>
+        <v>0.1906</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1768</v>
+        <v>-0.2302</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1602</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1899</v>
+        <v>-3.1969</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5857</v>
+        <v>-2.8333</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6042</v>
+        <v>-0.3636</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9255</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>0.011</v>
+        <v>0.004</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5087</v>
+        <v>0.2611</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4977</v>
+        <v>-0.2572</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8837</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.7451</v>
+        <v>-4.2194</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.8003</v>
+        <v>-2.622</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9449</v>
+        <v>-1.5974</v>
       </c>
       <c r="G9" t="n">
         <v>-3.4419</v>
@@ -1156,13 +1156,13 @@
         <v>1.5668</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.324</v>
+        <v>-0.7982</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0853</v>
+        <v>0.0929</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.2387</v>
+        <v>-0.8912</v>
       </c>
       <c r="V9" t="n">
         <v>0.6083</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.6325</v>
+        <v>-5.9426</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.7731</v>
+        <v>-6.0832</v>
       </c>
       <c r="F10" t="n">
         <v>0.1406</v>
@@ -1234,10 +1234,10 @@
         <v>1.9585</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2874</v>
+        <v>-0.5975</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7852</v>
+        <v>-0.0953</v>
       </c>
       <c r="U10" t="n">
         <v>-0.5023</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.642</v>
+        <v>-6.0988</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.3211</v>
+        <v>-4.9382</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.321</v>
+        <v>-1.1606</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8434</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0152</v>
+        <v>-0.472</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4705</v>
+        <v>-0.0876</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5447</v>
+        <v>-0.3843</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-19.9076</v>
+        <v>-19.0166</v>
       </c>
       <c r="E12" t="n">
-        <v>-17.6861</v>
+        <v>-16.7947</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.221699999999999</v>
+        <v>-2.2218</v>
       </c>
       <c r="G12" t="n">
         <v>-14.5355</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3384</v>
+        <v>-0.3383999999999998</v>
       </c>
       <c r="I12" t="n">
         <v>-14.1972</v>
@@ -1390,13 +1390,13 @@
         <v>10.7716</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.255500000000001</v>
+        <v>-1.3643</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2233000000000001</v>
+        <v>1.1145</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4791</v>
+        <v>-2.479</v>
       </c>
       <c r="V12" t="n">
         <v>1.7798</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3802</v>
+        <v>7.4724</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7779</v>
+        <v>4.5732</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6024</v>
+        <v>2.8992</v>
       </c>
       <c r="G13" t="n">
         <v>4.3049</v>
@@ -1468,13 +1468,13 @@
         <v>2.3502</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7827</v>
+        <v>0.8748</v>
       </c>
       <c r="T13" t="n">
-        <v>0.894</v>
+        <v>0.6893</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1113</v>
+        <v>0.1856</v>
       </c>
       <c r="V13" t="n">
         <v>-0.0576</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1484</v>
+        <v>6.013</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0461</v>
+        <v>3.1484</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1023</v>
+        <v>2.8646</v>
       </c>
       <c r="G14" t="n">
         <v>4.5669</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9144</v>
+        <v>0.779</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2535</v>
+        <v>0.3558</v>
       </c>
       <c r="U14" t="n">
-        <v>0.661</v>
+        <v>0.4232</v>
       </c>
       <c r="V14" t="n">
         <v>0.2754</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CAMBON DOMINGUEZ</t>
+          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.047</v>
+        <v>5.8623</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9466</v>
+        <v>3.5113</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1005</v>
+        <v>2.351</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6914</v>
+        <v>3.8029</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3981</v>
+        <v>3.8841</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2933</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4499</v>
+        <v>3.5728</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8492</v>
+        <v>3.6747</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3993</v>
+        <v>-0.102</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2415</v>
+        <v>0.2301</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.2094</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6926</v>
+        <v>0.0208</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6885</v>
+        <v>0.3544</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7881</v>
+        <v>0.0917</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.2626</v>
       </c>
       <c r="V15" t="n">
-        <v>1.492</v>
+        <v>-0.0576</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7086</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BADDINI GABRIOTTI RODRIGUES</t>
+          <t>M. CAMBON DOMINGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.4398</v>
+        <v>5.7474</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3856</v>
+        <v>4.5372</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0541</v>
+        <v>1.2102</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8029</v>
+        <v>2.6914</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8841</v>
+        <v>2.3981</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.2933</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5728</v>
+        <v>1.4499</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6747</v>
+        <v>1.8492</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.102</v>
+        <v>-0.3993</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2301</v>
+        <v>1.2415</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2094</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0208</v>
+        <v>0.6926</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0682</v>
+        <v>0.3889</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0339</v>
+        <v>0.3788</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0342</v>
+        <v>0.0102</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0576</v>
+        <v>1.492</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8260999999999999</v>
+        <v>2.7086</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8837</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GONZALEZ GARCIA</t>
+          <t>H. SANCHEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8606</v>
+        <v>3.5699</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3218</v>
+        <v>0.8056</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5388</v>
+        <v>2.7643</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8512</v>
+        <v>2.328</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.2758</v>
+        <v>-0.2837</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4245</v>
+        <v>2.6118</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.521</v>
+        <v>0.672</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1217</v>
+        <v>-1.242</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3993</v>
+        <v>1.914</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3302</v>
+        <v>1.6561</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1541</v>
+        <v>0.9583</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8239</v>
+        <v>0.6978</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2833</v>
+        <v>-0.4045</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8429</v>
+        <v>-0.1417</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4405</v>
+        <v>-0.2627</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6659</v>
+        <v>0.2754</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6659</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. SANCHEZ EXPOSITO</t>
+          <t>G. GONZALEZ GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4913</v>
+        <v>0.9105</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2939</v>
+        <v>-1.4412</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1973</v>
+        <v>2.3517</v>
       </c>
       <c r="G18" t="n">
-        <v>2.328</v>
+        <v>-2.8512</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2837</v>
+        <v>-3.2758</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6118</v>
+        <v>0.4245</v>
       </c>
       <c r="J18" t="n">
-        <v>0.672</v>
+        <v>-2.521</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.242</v>
+        <v>-2.1217</v>
       </c>
       <c r="L18" t="n">
-        <v>1.914</v>
+        <v>-0.3993</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6561</v>
+        <v>-0.3302</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9583</v>
+        <v>-1.1541</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6978</v>
+        <v>0.8239</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4831</v>
+        <v>1.3332</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6534</v>
+        <v>1.0798</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8297</v>
+        <v>0.2533</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2754</v>
+        <v>0.6659</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.237</v>
+        <v>0.2823</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8963</v>
+        <v>-1.5893</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1333</v>
+        <v>1.8716</v>
       </c>
       <c r="G19" t="n">
         <v>1.6124</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6246</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0465</v>
+        <v>0.3535</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.3164</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1654</v>
+        <v>-1.3359</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2083</v>
+        <v>-2.5153</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0429</v>
+        <v>1.1794</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2652</v>
@@ -2092,13 +2092,13 @@
         <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0176</v>
+        <v>-0.1882</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1476</v>
+        <v>-0.1594</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1653</v>
+        <v>-0.0288</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2742</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7692</v>
+        <v>-2.0216</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8013</v>
+        <v>-2.1873</v>
       </c>
       <c r="F22" t="n">
-        <v>0.032</v>
+        <v>0.1657</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9935</v>
@@ -2170,13 +2170,13 @@
         <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6767</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.517</v>
+        <v>0.097</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1597</v>
+        <v>-0.026</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8825</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8713</v>
+        <v>-5.3373</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.5659</v>
+        <v>-6.5426</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6946</v>
+        <v>1.2053</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6336000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.3709</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7331</v>
+        <v>-0.1991</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1704</v>
+        <v>-0.147</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5627</v>
+        <v>-0.052</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>19.9076</v>
+        <v>21.27220000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.221700000000001</v>
+        <v>2.2216</v>
       </c>
       <c r="F24" t="n">
-        <v>17.6857</v>
+        <v>19.0505</v>
       </c>
       <c r="G24" t="n">
         <v>14.5357</v>
@@ -2326,13 +2326,13 @@
         <v>15.6678</v>
       </c>
       <c r="S24" t="n">
-        <v>2.255399999999999</v>
+        <v>3.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.4791</v>
+        <v>2.479</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2235</v>
+        <v>1.1412</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7798</v>
